--- a/Tools/Luban/DataTables/Datas/CozyYard/recipe.xlsx
+++ b/Tools/Luban/DataTables/Datas/CozyYard/recipe.xlsx
@@ -30,7 +30,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,9 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -432,11 +441,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
@@ -496,157 +505,171 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>需要设施ID</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>输入物品ID列表</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>输入数量列表</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>输出物品ID</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>输出数量</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>制作时间(分钟)</t>
         </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>桂花干</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>4001</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>糯米粉</t>
+          <t>桂花干</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>桂花糕</t>
+          <t>糯米粉</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4001,4002</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5001</v>
+        <v>4002</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>辣炒蛋</t>
+          <t>桂花糕</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -654,32 +677,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3101,3005</t>
+          <t>4001,4002</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>清炒白菜</t>
+          <t>辣炒蛋</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -687,65 +710,65 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3101,3005</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>萝卜干</t>
+          <t>清炒白菜</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5003</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>20</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4003</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>菊花干</t>
+          <t>萝卜干</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -753,16 +776,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -774,66 +797,99 @@
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>菊花茶</t>
+          <t>菊花干</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5004</v>
+        <v>4004</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>菊花茶</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5004</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="n">
         <v>9</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>柿饼</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>20</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>3007</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>5005</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>180</v>
       </c>
     </row>
